--- a/config/企业列表.xlsx
+++ b/config/企业列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/samsung/Sources/qiuzhijia/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D671558-5F96-8B44-B881-34F126A7250C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC34261-34B1-6646-AB69-18BA45BCBA5E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-50020" yWindow="600" windowWidth="50020" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全局设置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12904" uniqueCount="5011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12905" uniqueCount="5011">
   <si>
     <t>所在省</t>
   </si>
@@ -33945,19 +33945,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -34565,18 +34565,21 @@
       <c r="A2" s="3" t="s">
         <v>3673</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>3673</v>
+      </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="36" t="s">
         <v>3600</v>
       </c>
       <c r="B3" s="32" t="s">
         <v>4988</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="36" t="s">
         <v>4894</v>
       </c>
-      <c r="D3" s="34">
+      <c r="D3" s="37">
         <v>3</v>
       </c>
       <c r="E3" s="38" t="s">
@@ -34584,41 +34587,41 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="35"/>
+      <c r="A4" s="36"/>
       <c r="B4" s="32" t="s">
         <v>3600</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="34"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="37"/>
       <c r="E4" s="38"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="35"/>
+      <c r="A5" s="36"/>
       <c r="B5" s="32" t="s">
         <v>4989</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="34"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="37"/>
       <c r="E5" s="38"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="35"/>
+      <c r="A6" s="36"/>
       <c r="B6" s="32" t="s">
         <v>3562</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="34"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="37"/>
       <c r="E6" s="38"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="36" t="s">
         <v>3599</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>3631</v>
       </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="34">
+      <c r="C7" s="36"/>
+      <c r="D7" s="37">
         <v>3</v>
       </c>
       <c r="E7" s="38" t="s">
@@ -34626,32 +34629,32 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="35"/>
+      <c r="A8" s="36"/>
       <c r="B8" s="32" t="s">
         <v>3597</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="34"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="37"/>
       <c r="E8" s="38"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="35"/>
+      <c r="A9" s="36"/>
       <c r="B9" s="32" t="s">
         <v>3599</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="34"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="37"/>
       <c r="E9" s="38"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="36" t="s">
         <v>4893</v>
       </c>
       <c r="B10" s="32" t="s">
         <v>4893</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="34">
+      <c r="C10" s="36"/>
+      <c r="D10" s="37">
         <v>4</v>
       </c>
       <c r="E10" s="38" t="s">
@@ -34659,25 +34662,25 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="35"/>
+      <c r="A11" s="36"/>
       <c r="B11" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="34"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="37"/>
       <c r="E11" s="38"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="36" t="s">
         <v>3556</v>
       </c>
       <c r="B12" s="32" t="s">
         <v>4954</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="36" t="s">
         <v>4879</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="37">
         <v>6</v>
       </c>
       <c r="E12" s="38" t="s">
@@ -34685,32 +34688,32 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="35"/>
+      <c r="A13" s="36"/>
       <c r="B13" s="32" t="s">
         <v>3556</v>
       </c>
-      <c r="C13" s="35"/>
-      <c r="D13" s="34"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="37"/>
       <c r="E13" s="38"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="35"/>
+      <c r="A14" s="36"/>
       <c r="B14" s="32" t="s">
         <v>4955</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="34"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="37"/>
       <c r="E14" s="38"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="36" t="s">
         <v>4896</v>
       </c>
       <c r="B15" s="32" t="s">
         <v>3676</v>
       </c>
-      <c r="C15" s="35"/>
-      <c r="D15" s="37">
+      <c r="C15" s="36"/>
+      <c r="D15" s="39">
         <v>6</v>
       </c>
       <c r="E15" s="38" t="s">
@@ -34718,113 +34721,113 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="35"/>
+      <c r="A16" s="36"/>
       <c r="B16" s="32" t="s">
         <v>3588</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="37"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="39"/>
       <c r="E16" s="38"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="35"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="32" t="s">
         <v>4967</v>
       </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="37"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="39"/>
       <c r="E17" s="38"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="35"/>
+      <c r="A18" s="36"/>
       <c r="B18" s="32" t="s">
         <v>4968</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="37"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="39"/>
       <c r="E18" s="38"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="35"/>
+      <c r="A19" s="36"/>
       <c r="B19" s="32" t="s">
         <v>4969</v>
       </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="37"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="39"/>
       <c r="E19" s="38"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="35"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="32" t="s">
         <v>3610</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="37"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="39"/>
       <c r="E20" s="38"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="35"/>
+      <c r="A21" s="36"/>
       <c r="B21" s="32" t="s">
         <v>4970</v>
       </c>
-      <c r="C21" s="35"/>
-      <c r="D21" s="37"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="39"/>
       <c r="E21" s="38"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="35"/>
+      <c r="A22" s="36"/>
       <c r="B22" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="37"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="39"/>
       <c r="E22" s="38"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="35"/>
+      <c r="A23" s="36"/>
       <c r="B23" s="32" t="s">
         <v>4971</v>
       </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="37"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="39"/>
       <c r="E23" s="38"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="35"/>
+      <c r="A24" s="36"/>
       <c r="B24" s="32" t="s">
         <v>4972</v>
       </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="37"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="39"/>
       <c r="E24" s="38"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="35"/>
+      <c r="A25" s="36"/>
       <c r="B25" s="32" t="s">
         <v>3578</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="37"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="39"/>
       <c r="E25" s="38"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="35"/>
+      <c r="A26" s="36"/>
       <c r="B26" s="32" t="s">
         <v>484</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="37"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="39"/>
       <c r="E26" s="38"/>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="35" t="s">
+      <c r="A27" s="36" t="s">
         <v>4942</v>
       </c>
       <c r="B27" s="32" t="s">
         <v>3595</v>
       </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="34">
+      <c r="C27" s="36"/>
+      <c r="D27" s="37">
         <v>6</v>
       </c>
       <c r="E27" s="38" t="s">
@@ -34832,43 +34835,43 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="35"/>
+      <c r="A28" s="36"/>
       <c r="B28" s="32" t="s">
         <v>5004</v>
       </c>
-      <c r="C28" s="35"/>
-      <c r="D28" s="34"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="37"/>
       <c r="E28" s="38"/>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="35"/>
+      <c r="A29" s="36"/>
       <c r="B29" s="32" t="s">
         <v>3576</v>
       </c>
-      <c r="C29" s="35"/>
-      <c r="D29" s="34"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="37"/>
       <c r="E29" s="38"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="35"/>
+      <c r="A30" s="36"/>
       <c r="B30" s="32" t="s">
         <v>3587</v>
       </c>
-      <c r="C30" s="35"/>
-      <c r="D30" s="34"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="37"/>
       <c r="E30" s="38"/>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="36" t="s">
         <v>4873</v>
       </c>
       <c r="B31" s="32" t="s">
         <v>3585</v>
       </c>
-      <c r="C31" s="35" t="s">
+      <c r="C31" s="36" t="s">
         <v>4874</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="37">
         <v>7</v>
       </c>
       <c r="E31" s="38" t="s">
@@ -34876,41 +34879,41 @@
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="35"/>
+      <c r="A32" s="36"/>
       <c r="B32" s="32" t="s">
         <v>4951</v>
       </c>
-      <c r="C32" s="35"/>
-      <c r="D32" s="34"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="37"/>
       <c r="E32" s="38"/>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="35"/>
+      <c r="A33" s="36"/>
       <c r="B33" s="32" t="s">
         <v>4952</v>
       </c>
-      <c r="C33" s="35"/>
-      <c r="D33" s="34"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="37"/>
       <c r="E33" s="38"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="35"/>
+      <c r="A34" s="36"/>
       <c r="B34" s="32" t="s">
         <v>485</v>
       </c>
-      <c r="C34" s="35"/>
-      <c r="D34" s="34"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="37"/>
       <c r="E34" s="38"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="35" t="s">
+      <c r="A35" s="36" t="s">
         <v>3563</v>
       </c>
       <c r="B35" s="32" t="s">
         <v>3589</v>
       </c>
-      <c r="C35" s="35"/>
-      <c r="D35" s="34">
+      <c r="C35" s="36"/>
+      <c r="D35" s="37">
         <v>3</v>
       </c>
       <c r="E35" s="38" t="s">
@@ -34918,23 +34921,23 @@
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="35"/>
+      <c r="A36" s="36"/>
       <c r="B36" s="32" t="s">
         <v>3563</v>
       </c>
-      <c r="C36" s="35"/>
-      <c r="D36" s="34"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="37"/>
       <c r="E36" s="38"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="35" t="s">
+      <c r="A37" s="36" t="s">
         <v>4877</v>
       </c>
       <c r="B37" s="32" t="s">
         <v>4953</v>
       </c>
-      <c r="C37" s="35"/>
-      <c r="D37" s="34">
+      <c r="C37" s="36"/>
+      <c r="D37" s="37">
         <v>7</v>
       </c>
       <c r="E37" s="38" t="s">
@@ -34942,23 +34945,23 @@
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="35"/>
+      <c r="A38" s="36"/>
       <c r="B38" s="32" t="s">
         <v>3564</v>
       </c>
-      <c r="C38" s="35"/>
-      <c r="D38" s="34"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="37"/>
       <c r="E38" s="38"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="35" t="s">
+      <c r="A39" s="36" t="s">
         <v>4881</v>
       </c>
       <c r="B39" s="32" t="s">
         <v>3635</v>
       </c>
-      <c r="C39" s="35"/>
-      <c r="D39" s="34">
+      <c r="C39" s="36"/>
+      <c r="D39" s="37">
         <v>4</v>
       </c>
       <c r="E39" s="38" t="s">
@@ -34966,32 +34969,32 @@
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="35"/>
+      <c r="A40" s="36"/>
       <c r="B40" s="32" t="s">
         <v>4881</v>
       </c>
-      <c r="C40" s="35"/>
-      <c r="D40" s="34"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="37"/>
       <c r="E40" s="38"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="35"/>
+      <c r="A41" s="36"/>
       <c r="B41" s="32" t="s">
         <v>3611</v>
       </c>
-      <c r="C41" s="35"/>
-      <c r="D41" s="34"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="37"/>
       <c r="E41" s="38"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="35" t="s">
+      <c r="A42" s="36" t="s">
         <v>4886</v>
       </c>
       <c r="B42" s="32" t="s">
         <v>3566</v>
       </c>
-      <c r="C42" s="35"/>
-      <c r="D42" s="34">
+      <c r="C42" s="36"/>
+      <c r="D42" s="37">
         <v>4</v>
       </c>
       <c r="E42" s="38" t="s">
@@ -34999,41 +35002,41 @@
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="35"/>
+      <c r="A43" s="36"/>
       <c r="B43" s="32" t="s">
         <v>3621</v>
       </c>
-      <c r="C43" s="35"/>
-      <c r="D43" s="34"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="37"/>
       <c r="E43" s="38"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="35"/>
+      <c r="A44" s="36"/>
       <c r="B44" s="32" t="s">
         <v>3616</v>
       </c>
-      <c r="C44" s="35"/>
-      <c r="D44" s="34"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="37"/>
       <c r="E44" s="38"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="35"/>
+      <c r="A45" s="36"/>
       <c r="B45" s="32" t="s">
         <v>3583</v>
       </c>
-      <c r="C45" s="35"/>
-      <c r="D45" s="34"/>
+      <c r="C45" s="36"/>
+      <c r="D45" s="37"/>
       <c r="E45" s="38"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="35" t="s">
+      <c r="A46" s="36" t="s">
         <v>3561</v>
       </c>
       <c r="B46" s="32" t="s">
         <v>4964</v>
       </c>
-      <c r="C46" s="35"/>
-      <c r="D46" s="34">
+      <c r="C46" s="36"/>
+      <c r="D46" s="37">
         <v>8</v>
       </c>
       <c r="E46" s="38" t="s">
@@ -35041,41 +35044,41 @@
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="35"/>
+      <c r="A47" s="36"/>
       <c r="B47" s="32" t="s">
         <v>3674</v>
       </c>
-      <c r="C47" s="35"/>
-      <c r="D47" s="34"/>
+      <c r="C47" s="36"/>
+      <c r="D47" s="37"/>
       <c r="E47" s="38"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="35"/>
+      <c r="A48" s="36"/>
       <c r="B48" s="32" t="s">
         <v>4965</v>
       </c>
-      <c r="C48" s="35"/>
-      <c r="D48" s="34"/>
+      <c r="C48" s="36"/>
+      <c r="D48" s="37"/>
       <c r="E48" s="38"/>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="35"/>
+      <c r="A49" s="36"/>
       <c r="B49" s="32" t="s">
         <v>3561</v>
       </c>
-      <c r="C49" s="35"/>
-      <c r="D49" s="34"/>
+      <c r="C49" s="36"/>
+      <c r="D49" s="37"/>
       <c r="E49" s="38"/>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="35" t="s">
+      <c r="A50" s="36" t="s">
         <v>3569</v>
       </c>
       <c r="B50" s="32" t="s">
         <v>3629</v>
       </c>
-      <c r="C50" s="35"/>
-      <c r="D50" s="34">
+      <c r="C50" s="36"/>
+      <c r="D50" s="37">
         <v>8</v>
       </c>
       <c r="E50" s="38" t="s">
@@ -35083,59 +35086,59 @@
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="35"/>
+      <c r="A51" s="36"/>
       <c r="B51" s="32" t="s">
         <v>4966</v>
       </c>
-      <c r="C51" s="35"/>
-      <c r="D51" s="34"/>
+      <c r="C51" s="36"/>
+      <c r="D51" s="37"/>
       <c r="E51" s="38"/>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="35"/>
+      <c r="A52" s="36"/>
       <c r="B52" s="32" t="s">
         <v>3569</v>
       </c>
-      <c r="C52" s="35"/>
-      <c r="D52" s="34"/>
+      <c r="C52" s="36"/>
+      <c r="D52" s="37"/>
       <c r="E52" s="38"/>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="35"/>
+      <c r="A53" s="36"/>
       <c r="B53" s="32" t="s">
         <v>3634</v>
       </c>
-      <c r="C53" s="35"/>
-      <c r="D53" s="34"/>
+      <c r="C53" s="36"/>
+      <c r="D53" s="37"/>
       <c r="E53" s="38"/>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="35"/>
+      <c r="A54" s="36"/>
       <c r="B54" s="32" t="s">
         <v>3572</v>
       </c>
-      <c r="C54" s="35"/>
-      <c r="D54" s="34"/>
+      <c r="C54" s="36"/>
+      <c r="D54" s="37"/>
       <c r="E54" s="38"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="35"/>
+      <c r="A55" s="36"/>
       <c r="B55" s="32" t="s">
         <v>3630</v>
       </c>
-      <c r="C55" s="35"/>
-      <c r="D55" s="34"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="37"/>
       <c r="E55" s="38"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="35" t="s">
+      <c r="A56" s="36" t="s">
         <v>4901</v>
       </c>
       <c r="B56" s="32" t="s">
         <v>3567</v>
       </c>
-      <c r="C56" s="35"/>
-      <c r="D56" s="37">
+      <c r="C56" s="36"/>
+      <c r="D56" s="39">
         <v>7</v>
       </c>
       <c r="E56" s="38" t="s">
@@ -35143,12 +35146,12 @@
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="35"/>
+      <c r="A57" s="36"/>
       <c r="B57" s="32" t="s">
         <v>3626</v>
       </c>
-      <c r="C57" s="35"/>
-      <c r="D57" s="37"/>
+      <c r="C57" s="36"/>
+      <c r="D57" s="39"/>
       <c r="E57" s="38"/>
     </row>
     <row r="58" spans="1:5" ht="48">
@@ -35158,11 +35161,11 @@
       <c r="B58" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="C58" s="35"/>
-      <c r="D58" s="36">
+      <c r="C58" s="36"/>
+      <c r="D58" s="34">
         <v>2</v>
       </c>
-      <c r="E58" s="39" t="s">
+      <c r="E58" s="35" t="s">
         <v>4904</v>
       </c>
     </row>
@@ -35173,23 +35176,23 @@
       <c r="B59" s="32" t="s">
         <v>3613</v>
       </c>
-      <c r="C59" s="35"/>
-      <c r="D59" s="36">
+      <c r="C59" s="36"/>
+      <c r="D59" s="34">
         <v>7</v>
       </c>
-      <c r="E59" s="39" t="s">
+      <c r="E59" s="35" t="s">
         <v>4906</v>
       </c>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="35" t="s">
+      <c r="A60" s="36" t="s">
         <v>4907</v>
       </c>
       <c r="B60" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="C60" s="35"/>
-      <c r="D60" s="37">
+      <c r="C60" s="36"/>
+      <c r="D60" s="39">
         <v>7</v>
       </c>
       <c r="E60" s="38" t="s">
@@ -35197,77 +35200,77 @@
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="35"/>
+      <c r="A61" s="36"/>
       <c r="B61" s="32" t="s">
         <v>3624</v>
       </c>
-      <c r="C61" s="35"/>
-      <c r="D61" s="37"/>
+      <c r="C61" s="36"/>
+      <c r="D61" s="39"/>
       <c r="E61" s="38"/>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="35"/>
+      <c r="A62" s="36"/>
       <c r="B62" s="32" t="s">
         <v>3633</v>
       </c>
-      <c r="C62" s="35"/>
-      <c r="D62" s="37"/>
+      <c r="C62" s="36"/>
+      <c r="D62" s="39"/>
       <c r="E62" s="38"/>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="35"/>
+      <c r="A63" s="36"/>
       <c r="B63" s="32" t="s">
         <v>3570</v>
       </c>
-      <c r="C63" s="35"/>
-      <c r="D63" s="37"/>
+      <c r="C63" s="36"/>
+      <c r="D63" s="39"/>
       <c r="E63" s="38"/>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="35"/>
+      <c r="A64" s="36"/>
       <c r="B64" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="C64" s="35"/>
-      <c r="D64" s="37"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="39"/>
       <c r="E64" s="38"/>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="35"/>
+      <c r="A65" s="36"/>
       <c r="B65" s="32" t="s">
         <v>4976</v>
       </c>
-      <c r="C65" s="35"/>
-      <c r="D65" s="37"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="39"/>
       <c r="E65" s="38"/>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="35"/>
+      <c r="A66" s="36"/>
       <c r="B66" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="C66" s="35"/>
-      <c r="D66" s="37"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="39"/>
       <c r="E66" s="38"/>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="35"/>
+      <c r="A67" s="36"/>
       <c r="B67" s="32" t="s">
         <v>3558</v>
       </c>
-      <c r="C67" s="35"/>
-      <c r="D67" s="37"/>
+      <c r="C67" s="36"/>
+      <c r="D67" s="39"/>
       <c r="E67" s="38"/>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="35" t="s">
+      <c r="A68" s="36" t="s">
         <v>3568</v>
       </c>
       <c r="B68" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C68" s="35"/>
-      <c r="D68" s="34">
+      <c r="C68" s="36"/>
+      <c r="D68" s="37">
         <v>10</v>
       </c>
       <c r="E68" s="38" t="s">
@@ -35275,86 +35278,86 @@
       </c>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="35"/>
+      <c r="A69" s="36"/>
       <c r="B69" s="32" t="s">
         <v>3628</v>
       </c>
-      <c r="C69" s="35"/>
-      <c r="D69" s="34"/>
+      <c r="C69" s="36"/>
+      <c r="D69" s="37"/>
       <c r="E69" s="38"/>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="35"/>
+      <c r="A70" s="36"/>
       <c r="B70" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="C70" s="35"/>
-      <c r="D70" s="34"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="37"/>
       <c r="E70" s="38"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="35"/>
+      <c r="A71" s="36"/>
       <c r="B71" s="32" t="s">
         <v>3568</v>
       </c>
-      <c r="C71" s="35"/>
-      <c r="D71" s="34"/>
+      <c r="C71" s="36"/>
+      <c r="D71" s="37"/>
       <c r="E71" s="38"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="35"/>
+      <c r="A72" s="36"/>
       <c r="B72" s="32" t="s">
         <v>3627</v>
       </c>
-      <c r="C72" s="35"/>
-      <c r="D72" s="34"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="37"/>
       <c r="E72" s="38"/>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="35"/>
+      <c r="A73" s="36"/>
       <c r="B73" s="32" t="s">
         <v>3675</v>
       </c>
-      <c r="C73" s="35"/>
-      <c r="D73" s="34"/>
+      <c r="C73" s="36"/>
+      <c r="D73" s="37"/>
       <c r="E73" s="38"/>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="35"/>
+      <c r="A74" s="36"/>
       <c r="B74" s="32" t="s">
         <v>3625</v>
       </c>
-      <c r="C74" s="35"/>
-      <c r="D74" s="34"/>
+      <c r="C74" s="36"/>
+      <c r="D74" s="37"/>
       <c r="E74" s="38"/>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="35"/>
+      <c r="A75" s="36"/>
       <c r="B75" s="32" t="s">
         <v>3574</v>
       </c>
-      <c r="C75" s="35"/>
-      <c r="D75" s="34"/>
+      <c r="C75" s="36"/>
+      <c r="D75" s="37"/>
       <c r="E75" s="38"/>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="35"/>
+      <c r="A76" s="36"/>
       <c r="B76" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="C76" s="35"/>
-      <c r="D76" s="34"/>
+      <c r="C76" s="36"/>
+      <c r="D76" s="37"/>
       <c r="E76" s="38"/>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="35" t="s">
+      <c r="A77" s="36" t="s">
         <v>4910</v>
       </c>
       <c r="B77" s="32" t="s">
         <v>3581</v>
       </c>
-      <c r="C77" s="35"/>
-      <c r="D77" s="34">
+      <c r="C77" s="36"/>
+      <c r="D77" s="37">
         <v>7</v>
       </c>
       <c r="E77" s="38" t="s">
@@ -35362,41 +35365,41 @@
       </c>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="35"/>
+      <c r="A78" s="36"/>
       <c r="B78" s="32" t="s">
         <v>3608</v>
       </c>
-      <c r="C78" s="35"/>
-      <c r="D78" s="34"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="37"/>
       <c r="E78" s="38"/>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="35"/>
+      <c r="A79" s="36"/>
       <c r="B79" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="35"/>
-      <c r="D79" s="34"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="37"/>
       <c r="E79" s="38"/>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="35"/>
+      <c r="A80" s="36"/>
       <c r="B80" s="32" t="s">
         <v>3612</v>
       </c>
-      <c r="C80" s="35"/>
-      <c r="D80" s="34"/>
+      <c r="C80" s="36"/>
+      <c r="D80" s="37"/>
       <c r="E80" s="38"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="35" t="s">
+      <c r="A81" s="36" t="s">
         <v>4916</v>
       </c>
       <c r="B81" s="33" t="s">
         <v>4980</v>
       </c>
-      <c r="C81" s="35"/>
-      <c r="D81" s="34">
+      <c r="C81" s="36"/>
+      <c r="D81" s="37">
         <v>4</v>
       </c>
       <c r="E81" s="38" t="s">
@@ -35404,41 +35407,41 @@
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="35"/>
+      <c r="A82" s="36"/>
       <c r="B82" s="33" t="s">
         <v>4981</v>
       </c>
-      <c r="C82" s="35"/>
-      <c r="D82" s="34"/>
+      <c r="C82" s="36"/>
+      <c r="D82" s="37"/>
       <c r="E82" s="38"/>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="35"/>
+      <c r="A83" s="36"/>
       <c r="B83" s="33" t="s">
         <v>4982</v>
       </c>
-      <c r="C83" s="35"/>
-      <c r="D83" s="34"/>
+      <c r="C83" s="36"/>
+      <c r="D83" s="37"/>
       <c r="E83" s="38"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="35"/>
+      <c r="A84" s="36"/>
       <c r="B84" s="33" t="s">
         <v>3580</v>
       </c>
-      <c r="C84" s="35"/>
-      <c r="D84" s="34"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="37"/>
       <c r="E84" s="38"/>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="35" t="s">
+      <c r="A85" s="36" t="s">
         <v>4921</v>
       </c>
       <c r="B85" s="32" t="s">
         <v>3555</v>
       </c>
-      <c r="C85" s="35"/>
-      <c r="D85" s="34">
+      <c r="C85" s="36"/>
+      <c r="D85" s="37">
         <v>8</v>
       </c>
       <c r="E85" s="38" t="s">
@@ -35446,32 +35449,32 @@
       </c>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="35"/>
+      <c r="A86" s="36"/>
       <c r="B86" s="32" t="s">
         <v>3623</v>
       </c>
-      <c r="C86" s="35"/>
-      <c r="D86" s="34"/>
+      <c r="C86" s="36"/>
+      <c r="D86" s="37"/>
       <c r="E86" s="38"/>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="35"/>
+      <c r="A87" s="36"/>
       <c r="B87" s="32" t="s">
         <v>3579</v>
       </c>
-      <c r="C87" s="35"/>
-      <c r="D87" s="34"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="37"/>
       <c r="E87" s="38"/>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="35" t="s">
+      <c r="A88" s="36" t="s">
         <v>3606</v>
       </c>
       <c r="B88" s="32" t="s">
         <v>3606</v>
       </c>
-      <c r="C88" s="35"/>
-      <c r="D88" s="34">
+      <c r="C88" s="36"/>
+      <c r="D88" s="37">
         <v>4</v>
       </c>
       <c r="E88" s="38" t="s">
@@ -35479,23 +35482,23 @@
       </c>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="35"/>
+      <c r="A89" s="36"/>
       <c r="B89" s="32" t="s">
         <v>4991</v>
       </c>
-      <c r="C89" s="35"/>
-      <c r="D89" s="34"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="37"/>
       <c r="E89" s="38"/>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="35" t="s">
+      <c r="A90" s="36" t="s">
         <v>80</v>
       </c>
       <c r="B90" s="32" t="s">
         <v>3565</v>
       </c>
-      <c r="C90" s="35"/>
-      <c r="D90" s="34">
+      <c r="C90" s="36"/>
+      <c r="D90" s="37">
         <v>5</v>
       </c>
       <c r="E90" s="38" t="s">
@@ -35503,120 +35506,120 @@
       </c>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="35"/>
+      <c r="A91" s="36"/>
       <c r="B91" s="32" t="s">
         <v>3615</v>
       </c>
-      <c r="C91" s="35"/>
-      <c r="D91" s="34"/>
+      <c r="C91" s="36"/>
+      <c r="D91" s="37"/>
       <c r="E91" s="38"/>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="35"/>
+      <c r="A92" s="36"/>
       <c r="B92" s="32" t="s">
         <v>4993</v>
       </c>
-      <c r="C92" s="35"/>
-      <c r="D92" s="34"/>
+      <c r="C92" s="36"/>
+      <c r="D92" s="37"/>
       <c r="E92" s="38"/>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="35"/>
+      <c r="A93" s="36"/>
       <c r="B93" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="C93" s="35"/>
-      <c r="D93" s="34"/>
+      <c r="C93" s="36"/>
+      <c r="D93" s="37"/>
       <c r="E93" s="38"/>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="35"/>
+      <c r="A94" s="36"/>
       <c r="B94" s="32" t="s">
         <v>4994</v>
       </c>
-      <c r="C94" s="35"/>
-      <c r="D94" s="34"/>
+      <c r="C94" s="36"/>
+      <c r="D94" s="37"/>
       <c r="E94" s="38"/>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="35"/>
+      <c r="A95" s="36"/>
       <c r="B95" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="C95" s="35"/>
-      <c r="D95" s="34"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="37"/>
       <c r="E95" s="38"/>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="35"/>
+      <c r="A96" s="36"/>
       <c r="B96" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="C96" s="35"/>
-      <c r="D96" s="34"/>
+      <c r="C96" s="36"/>
+      <c r="D96" s="37"/>
       <c r="E96" s="38"/>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="35"/>
+      <c r="A97" s="36"/>
       <c r="B97" s="32" t="s">
         <v>3582</v>
       </c>
-      <c r="C97" s="35"/>
-      <c r="D97" s="34"/>
+      <c r="C97" s="36"/>
+      <c r="D97" s="37"/>
       <c r="E97" s="38"/>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="35"/>
+      <c r="A98" s="36"/>
       <c r="B98" s="32" t="s">
         <v>4995</v>
       </c>
-      <c r="C98" s="35"/>
-      <c r="D98" s="34"/>
+      <c r="C98" s="36"/>
+      <c r="D98" s="37"/>
       <c r="E98" s="38"/>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="35"/>
+      <c r="A99" s="36"/>
       <c r="B99" s="32" t="s">
         <v>308</v>
       </c>
-      <c r="C99" s="35"/>
-      <c r="D99" s="34"/>
+      <c r="C99" s="36"/>
+      <c r="D99" s="37"/>
       <c r="E99" s="38"/>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="35"/>
+      <c r="A100" s="36"/>
       <c r="B100" s="32" t="s">
         <v>3557</v>
       </c>
-      <c r="C100" s="35"/>
-      <c r="D100" s="34"/>
+      <c r="C100" s="36"/>
+      <c r="D100" s="37"/>
       <c r="E100" s="38"/>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="35"/>
+      <c r="A101" s="36"/>
       <c r="B101" s="32" t="s">
         <v>4996</v>
       </c>
-      <c r="C101" s="35"/>
-      <c r="D101" s="34"/>
+      <c r="C101" s="36"/>
+      <c r="D101" s="37"/>
       <c r="E101" s="38"/>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="35"/>
+      <c r="A102" s="36"/>
       <c r="B102" s="32" t="s">
         <v>4997</v>
       </c>
-      <c r="C102" s="35"/>
-      <c r="D102" s="34"/>
+      <c r="C102" s="36"/>
+      <c r="D102" s="37"/>
       <c r="E102" s="38"/>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="35"/>
+      <c r="A103" s="36"/>
       <c r="B103" s="32" t="s">
         <v>4998</v>
       </c>
-      <c r="C103" s="35"/>
-      <c r="D103" s="34"/>
+      <c r="C103" s="36"/>
+      <c r="D103" s="37"/>
       <c r="E103" s="38"/>
     </row>
     <row r="104" spans="1:5" ht="48">
@@ -35626,11 +35629,11 @@
       <c r="B104" s="32" t="s">
         <v>5005</v>
       </c>
-      <c r="C104" s="35"/>
-      <c r="D104" s="36">
+      <c r="C104" s="36"/>
+      <c r="D104" s="34">
         <v>5</v>
       </c>
-      <c r="E104" s="39" t="s">
+      <c r="E104" s="35" t="s">
         <v>4946</v>
       </c>
     </row>
@@ -35641,11 +35644,11 @@
       <c r="B105" s="32" t="s">
         <v>3591</v>
       </c>
-      <c r="C105" s="35"/>
-      <c r="D105" s="36">
+      <c r="C105" s="36"/>
+      <c r="D105" s="34">
         <v>8</v>
       </c>
-      <c r="E105" s="39" t="s">
+      <c r="E105" s="35" t="s">
         <v>4948</v>
       </c>
     </row>
@@ -35656,13 +35659,13 @@
       <c r="B106" s="32" t="s">
         <v>3596</v>
       </c>
-      <c r="C106" s="35" t="s">
+      <c r="C106" s="36" t="s">
         <v>4912</v>
       </c>
-      <c r="D106" s="36">
+      <c r="D106" s="34">
         <v>4</v>
       </c>
-      <c r="E106" s="39" t="s">
+      <c r="E106" s="35" t="s">
         <v>4913</v>
       </c>
     </row>
@@ -35673,11 +35676,11 @@
       <c r="B107" s="32" t="s">
         <v>3607</v>
       </c>
-      <c r="C107" s="35"/>
-      <c r="D107" s="36">
+      <c r="C107" s="36"/>
+      <c r="D107" s="34">
         <v>4</v>
       </c>
-      <c r="E107" s="39" t="s">
+      <c r="E107" s="35" t="s">
         <v>4932</v>
       </c>
     </row>
@@ -35688,25 +35691,25 @@
       <c r="B108" s="32" t="s">
         <v>3602</v>
       </c>
-      <c r="C108" s="35"/>
-      <c r="D108" s="36">
+      <c r="C108" s="36"/>
+      <c r="D108" s="34">
         <v>4</v>
       </c>
-      <c r="E108" s="39" t="s">
+      <c r="E108" s="35" t="s">
         <v>4937</v>
       </c>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="35" t="s">
+      <c r="A109" s="36" t="s">
         <v>4898</v>
       </c>
       <c r="B109" s="32" t="s">
         <v>3590</v>
       </c>
-      <c r="C109" s="35" t="s">
+      <c r="C109" s="36" t="s">
         <v>4899</v>
       </c>
-      <c r="D109" s="34">
+      <c r="D109" s="37">
         <v>5</v>
       </c>
       <c r="E109" s="38" t="s">
@@ -35714,41 +35717,41 @@
       </c>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="35"/>
+      <c r="A110" s="36"/>
       <c r="B110" s="32" t="s">
         <v>4973</v>
       </c>
-      <c r="C110" s="35"/>
-      <c r="D110" s="34"/>
+      <c r="C110" s="36"/>
+      <c r="D110" s="37"/>
       <c r="E110" s="38"/>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="35"/>
+      <c r="A111" s="36"/>
       <c r="B111" s="32" t="s">
         <v>4974</v>
       </c>
-      <c r="C111" s="35"/>
-      <c r="D111" s="34"/>
+      <c r="C111" s="36"/>
+      <c r="D111" s="37"/>
       <c r="E111" s="38"/>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="35"/>
+      <c r="A112" s="36"/>
       <c r="B112" s="32" t="s">
         <v>4898</v>
       </c>
-      <c r="C112" s="35"/>
-      <c r="D112" s="34"/>
+      <c r="C112" s="36"/>
+      <c r="D112" s="37"/>
       <c r="E112" s="38"/>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="35" t="s">
+      <c r="A113" s="36" t="s">
         <v>4914</v>
       </c>
       <c r="B113" s="32" t="s">
         <v>3592</v>
       </c>
-      <c r="C113" s="35"/>
-      <c r="D113" s="34">
+      <c r="C113" s="36"/>
+      <c r="D113" s="37">
         <v>8</v>
       </c>
       <c r="E113" s="38" t="s">
@@ -35756,88 +35759,88 @@
       </c>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="35"/>
+      <c r="A114" s="36"/>
       <c r="B114" s="32" t="s">
         <v>4977</v>
       </c>
-      <c r="C114" s="35"/>
-      <c r="D114" s="34"/>
+      <c r="C114" s="36"/>
+      <c r="D114" s="37"/>
       <c r="E114" s="38"/>
     </row>
     <row r="115" spans="1:5">
-      <c r="A115" s="35"/>
+      <c r="A115" s="36"/>
       <c r="B115" s="32" t="s">
         <v>4978</v>
       </c>
-      <c r="C115" s="35"/>
-      <c r="D115" s="34"/>
+      <c r="C115" s="36"/>
+      <c r="D115" s="37"/>
       <c r="E115" s="38"/>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="35"/>
+      <c r="A116" s="36"/>
       <c r="B116" s="32" t="s">
         <v>3593</v>
       </c>
-      <c r="C116" s="35"/>
-      <c r="D116" s="34"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="37"/>
       <c r="E116" s="38"/>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="35"/>
+      <c r="A117" s="36"/>
       <c r="B117" s="32" t="s">
         <v>4914</v>
       </c>
-      <c r="C117" s="35"/>
-      <c r="D117" s="34"/>
+      <c r="C117" s="36"/>
+      <c r="D117" s="37"/>
       <c r="E117" s="38"/>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="35"/>
+      <c r="A118" s="36"/>
       <c r="B118" s="32" t="s">
         <v>469</v>
       </c>
-      <c r="C118" s="35"/>
-      <c r="D118" s="34"/>
+      <c r="C118" s="36"/>
+      <c r="D118" s="37"/>
       <c r="E118" s="38"/>
     </row>
     <row r="119" spans="1:5">
-      <c r="A119" s="35"/>
+      <c r="A119" s="36"/>
       <c r="B119" s="32" t="s">
         <v>3614</v>
       </c>
-      <c r="C119" s="35"/>
-      <c r="D119" s="34"/>
+      <c r="C119" s="36"/>
+      <c r="D119" s="37"/>
       <c r="E119" s="38"/>
     </row>
     <row r="120" spans="1:5">
-      <c r="A120" s="35"/>
+      <c r="A120" s="36"/>
       <c r="B120" s="32" t="s">
         <v>466</v>
       </c>
-      <c r="C120" s="35"/>
-      <c r="D120" s="34"/>
+      <c r="C120" s="36"/>
+      <c r="D120" s="37"/>
       <c r="E120" s="38"/>
     </row>
     <row r="121" spans="1:5">
-      <c r="A121" s="35"/>
+      <c r="A121" s="36"/>
       <c r="B121" s="32" t="s">
         <v>4979</v>
       </c>
-      <c r="C121" s="35"/>
-      <c r="D121" s="34"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="37"/>
       <c r="E121" s="38"/>
     </row>
     <row r="122" spans="1:5">
-      <c r="A122" s="35" t="s">
+      <c r="A122" s="36" t="s">
         <v>482</v>
       </c>
       <c r="B122" s="32" t="s">
         <v>4984</v>
       </c>
-      <c r="C122" s="35" t="s">
+      <c r="C122" s="36" t="s">
         <v>4919</v>
       </c>
-      <c r="D122" s="34">
+      <c r="D122" s="37">
         <v>2</v>
       </c>
       <c r="E122" s="38" t="s">
@@ -35845,25 +35848,25 @@
       </c>
     </row>
     <row r="123" spans="1:5">
-      <c r="A123" s="35"/>
+      <c r="A123" s="36"/>
       <c r="B123" s="32" t="s">
         <v>482</v>
       </c>
-      <c r="C123" s="35"/>
-      <c r="D123" s="34"/>
+      <c r="C123" s="36"/>
+      <c r="D123" s="37"/>
       <c r="E123" s="38"/>
     </row>
     <row r="124" spans="1:5">
-      <c r="A124" s="35" t="s">
+      <c r="A124" s="36" t="s">
         <v>4888</v>
       </c>
       <c r="B124" s="32" t="s">
         <v>3586</v>
       </c>
-      <c r="C124" s="35" t="s">
+      <c r="C124" s="36" t="s">
         <v>4889</v>
       </c>
-      <c r="D124" s="34">
+      <c r="D124" s="37">
         <v>3</v>
       </c>
       <c r="E124" s="38" t="s">
@@ -35871,77 +35874,77 @@
       </c>
     </row>
     <row r="125" spans="1:5">
-      <c r="A125" s="35"/>
+      <c r="A125" s="36"/>
       <c r="B125" s="32" t="s">
         <v>4959</v>
       </c>
-      <c r="C125" s="35"/>
-      <c r="D125" s="34"/>
+      <c r="C125" s="36"/>
+      <c r="D125" s="37"/>
       <c r="E125" s="38"/>
     </row>
     <row r="126" spans="1:5">
-      <c r="A126" s="35"/>
+      <c r="A126" s="36"/>
       <c r="B126" s="32" t="s">
         <v>3604</v>
       </c>
-      <c r="C126" s="35"/>
-      <c r="D126" s="34"/>
+      <c r="C126" s="36"/>
+      <c r="D126" s="37"/>
       <c r="E126" s="38"/>
     </row>
     <row r="127" spans="1:5">
-      <c r="A127" s="35"/>
+      <c r="A127" s="36"/>
       <c r="B127" s="32" t="s">
         <v>4960</v>
       </c>
-      <c r="C127" s="35"/>
-      <c r="D127" s="34"/>
+      <c r="C127" s="36"/>
+      <c r="D127" s="37"/>
       <c r="E127" s="38"/>
     </row>
     <row r="128" spans="1:5">
-      <c r="A128" s="35"/>
+      <c r="A128" s="36"/>
       <c r="B128" s="32" t="s">
         <v>4961</v>
       </c>
-      <c r="C128" s="35"/>
-      <c r="D128" s="34"/>
+      <c r="C128" s="36"/>
+      <c r="D128" s="37"/>
       <c r="E128" s="38"/>
     </row>
     <row r="129" spans="1:5">
-      <c r="A129" s="35"/>
+      <c r="A129" s="36"/>
       <c r="B129" s="32" t="s">
         <v>4962</v>
       </c>
-      <c r="C129" s="35"/>
-      <c r="D129" s="34"/>
+      <c r="C129" s="36"/>
+      <c r="D129" s="37"/>
       <c r="E129" s="38"/>
     </row>
     <row r="130" spans="1:5">
-      <c r="A130" s="35"/>
+      <c r="A130" s="36"/>
       <c r="B130" s="32" t="s">
         <v>3560</v>
       </c>
-      <c r="C130" s="35"/>
-      <c r="D130" s="34"/>
+      <c r="C130" s="36"/>
+      <c r="D130" s="37"/>
       <c r="E130" s="38"/>
     </row>
     <row r="131" spans="1:5">
-      <c r="A131" s="35"/>
+      <c r="A131" s="36"/>
       <c r="B131" s="32" t="s">
         <v>4963</v>
       </c>
-      <c r="C131" s="35"/>
-      <c r="D131" s="34"/>
+      <c r="C131" s="36"/>
+      <c r="D131" s="37"/>
       <c r="E131" s="38"/>
     </row>
     <row r="132" spans="1:5">
-      <c r="A132" s="35" t="s">
+      <c r="A132" s="36" t="s">
         <v>3571</v>
       </c>
       <c r="B132" s="32" t="s">
         <v>4975</v>
       </c>
-      <c r="C132" s="35"/>
-      <c r="D132" s="34">
+      <c r="C132" s="36"/>
+      <c r="D132" s="37">
         <v>5</v>
       </c>
       <c r="E132" s="38" t="s">
@@ -35949,32 +35952,32 @@
       </c>
     </row>
     <row r="133" spans="1:5">
-      <c r="A133" s="35"/>
+      <c r="A133" s="36"/>
       <c r="B133" s="32" t="s">
         <v>3559</v>
       </c>
-      <c r="C133" s="35"/>
-      <c r="D133" s="34"/>
+      <c r="C133" s="36"/>
+      <c r="D133" s="37"/>
       <c r="E133" s="38"/>
     </row>
     <row r="134" spans="1:5">
-      <c r="A134" s="35"/>
+      <c r="A134" s="36"/>
       <c r="B134" s="32" t="s">
         <v>3571</v>
       </c>
-      <c r="C134" s="35"/>
-      <c r="D134" s="34"/>
+      <c r="C134" s="36"/>
+      <c r="D134" s="37"/>
       <c r="E134" s="38"/>
     </row>
     <row r="135" spans="1:5">
-      <c r="A135" s="35" t="s">
+      <c r="A135" s="36" t="s">
         <v>83</v>
       </c>
       <c r="B135" s="32" t="s">
         <v>4983</v>
       </c>
-      <c r="C135" s="35"/>
-      <c r="D135" s="34">
+      <c r="C135" s="36"/>
+      <c r="D135" s="37">
         <v>6</v>
       </c>
       <c r="E135" s="38" t="s">
@@ -35982,32 +35985,32 @@
       </c>
     </row>
     <row r="136" spans="1:5">
-      <c r="A136" s="35"/>
+      <c r="A136" s="36"/>
       <c r="B136" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="C136" s="35"/>
-      <c r="D136" s="34"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="37"/>
       <c r="E136" s="38"/>
     </row>
     <row r="137" spans="1:5">
-      <c r="A137" s="35"/>
+      <c r="A137" s="36"/>
       <c r="B137" s="32" t="s">
         <v>3672</v>
       </c>
-      <c r="C137" s="35"/>
-      <c r="D137" s="34"/>
+      <c r="C137" s="36"/>
+      <c r="D137" s="37"/>
       <c r="E137" s="38"/>
     </row>
     <row r="138" spans="1:5">
-      <c r="A138" s="35" t="s">
+      <c r="A138" s="36" t="s">
         <v>4928</v>
       </c>
       <c r="B138" s="32" t="s">
         <v>3577</v>
       </c>
-      <c r="C138" s="35"/>
-      <c r="D138" s="34">
+      <c r="C138" s="36"/>
+      <c r="D138" s="37">
         <v>5</v>
       </c>
       <c r="E138" s="38" t="s">
@@ -36015,32 +36018,32 @@
       </c>
     </row>
     <row r="139" spans="1:5">
-      <c r="A139" s="35"/>
+      <c r="A139" s="36"/>
       <c r="B139" s="32" t="s">
         <v>4928</v>
       </c>
-      <c r="C139" s="35"/>
-      <c r="D139" s="34"/>
+      <c r="C139" s="36"/>
+      <c r="D139" s="37"/>
       <c r="E139" s="38"/>
     </row>
     <row r="140" spans="1:5">
-      <c r="A140" s="35"/>
+      <c r="A140" s="36"/>
       <c r="B140" s="32" t="s">
         <v>4990</v>
       </c>
-      <c r="C140" s="35"/>
-      <c r="D140" s="34"/>
+      <c r="C140" s="36"/>
+      <c r="D140" s="37"/>
       <c r="E140" s="38"/>
     </row>
     <row r="141" spans="1:5">
-      <c r="A141" s="35" t="s">
+      <c r="A141" s="36" t="s">
         <v>79</v>
       </c>
       <c r="B141" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="C141" s="35"/>
-      <c r="D141" s="34">
+      <c r="C141" s="36"/>
+      <c r="D141" s="37">
         <v>5</v>
       </c>
       <c r="E141" s="38" t="s">
@@ -36048,32 +36051,32 @@
       </c>
     </row>
     <row r="142" spans="1:5">
-      <c r="A142" s="35"/>
+      <c r="A142" s="36"/>
       <c r="B142" s="32" t="s">
         <v>4992</v>
       </c>
-      <c r="C142" s="35"/>
-      <c r="D142" s="34"/>
+      <c r="C142" s="36"/>
+      <c r="D142" s="37"/>
       <c r="E142" s="38"/>
     </row>
     <row r="143" spans="1:5">
-      <c r="A143" s="35"/>
+      <c r="A143" s="36"/>
       <c r="B143" s="32" t="s">
         <v>3620</v>
       </c>
-      <c r="C143" s="35"/>
-      <c r="D143" s="34"/>
+      <c r="C143" s="36"/>
+      <c r="D143" s="37"/>
       <c r="E143" s="38"/>
     </row>
     <row r="144" spans="1:5">
-      <c r="A144" s="35" t="s">
+      <c r="A144" s="36" t="s">
         <v>3575</v>
       </c>
       <c r="B144" s="32" t="s">
         <v>3573</v>
       </c>
-      <c r="C144" s="35"/>
-      <c r="D144" s="34">
+      <c r="C144" s="36"/>
+      <c r="D144" s="37">
         <v>5</v>
       </c>
       <c r="E144" s="38" t="s">
@@ -36081,34 +36084,34 @@
       </c>
     </row>
     <row r="145" spans="1:5">
-      <c r="A145" s="35"/>
+      <c r="A145" s="36"/>
       <c r="B145" s="32" t="s">
         <v>3575</v>
       </c>
-      <c r="C145" s="35"/>
-      <c r="D145" s="34"/>
+      <c r="C145" s="36"/>
+      <c r="D145" s="37"/>
       <c r="E145" s="38"/>
     </row>
     <row r="146" spans="1:5">
-      <c r="A146" s="35"/>
+      <c r="A146" s="36"/>
       <c r="B146" s="32" t="s">
         <v>4999</v>
       </c>
-      <c r="C146" s="35"/>
-      <c r="D146" s="34"/>
+      <c r="C146" s="36"/>
+      <c r="D146" s="37"/>
       <c r="E146" s="38"/>
     </row>
     <row r="147" spans="1:5">
-      <c r="A147" s="35" t="s">
+      <c r="A147" s="36" t="s">
         <v>487</v>
       </c>
       <c r="B147" s="32" t="s">
         <v>3636</v>
       </c>
-      <c r="C147" s="35" t="s">
+      <c r="C147" s="36" t="s">
         <v>4923</v>
       </c>
-      <c r="D147" s="34">
+      <c r="D147" s="37">
         <v>4</v>
       </c>
       <c r="E147" s="38" t="s">
@@ -36116,43 +36119,43 @@
       </c>
     </row>
     <row r="148" spans="1:5">
-      <c r="A148" s="35"/>
+      <c r="A148" s="36"/>
       <c r="B148" s="32" t="s">
         <v>3594</v>
       </c>
-      <c r="C148" s="35"/>
-      <c r="D148" s="34"/>
+      <c r="C148" s="36"/>
+      <c r="D148" s="37"/>
       <c r="E148" s="38"/>
     </row>
     <row r="149" spans="1:5">
-      <c r="A149" s="35"/>
+      <c r="A149" s="36"/>
       <c r="B149" s="32" t="s">
         <v>4985</v>
       </c>
-      <c r="C149" s="35"/>
-      <c r="D149" s="34"/>
+      <c r="C149" s="36"/>
+      <c r="D149" s="37"/>
       <c r="E149" s="38"/>
     </row>
     <row r="150" spans="1:5">
-      <c r="A150" s="35"/>
+      <c r="A150" s="36"/>
       <c r="B150" s="32" t="s">
         <v>487</v>
       </c>
-      <c r="C150" s="35"/>
-      <c r="D150" s="34"/>
+      <c r="C150" s="36"/>
+      <c r="D150" s="37"/>
       <c r="E150" s="38"/>
     </row>
     <row r="151" spans="1:5">
-      <c r="A151" s="35"/>
+      <c r="A151" s="36"/>
       <c r="B151" s="32" t="s">
         <v>486</v>
       </c>
-      <c r="C151" s="35"/>
-      <c r="D151" s="34"/>
+      <c r="C151" s="36"/>
+      <c r="D151" s="37"/>
       <c r="E151" s="38"/>
     </row>
     <row r="152" spans="1:5" ht="16" customHeight="1">
-      <c r="A152" s="35" t="s">
+      <c r="A152" s="36" t="s">
         <v>483</v>
       </c>
       <c r="B152" s="32" t="s">
@@ -36161,7 +36164,7 @@
       <c r="C152" s="38" t="s">
         <v>4884</v>
       </c>
-      <c r="D152" s="34">
+      <c r="D152" s="37">
         <v>3</v>
       </c>
       <c r="E152" s="38" t="s">
@@ -36169,32 +36172,32 @@
       </c>
     </row>
     <row r="153" spans="1:5">
-      <c r="A153" s="35"/>
+      <c r="A153" s="36"/>
       <c r="B153" s="32" t="s">
         <v>5007</v>
       </c>
       <c r="C153" s="38"/>
-      <c r="D153" s="34"/>
+      <c r="D153" s="37"/>
       <c r="E153" s="38"/>
     </row>
     <row r="154" spans="1:5">
-      <c r="A154" s="35"/>
+      <c r="A154" s="36"/>
       <c r="B154" s="32" t="s">
         <v>483</v>
       </c>
       <c r="C154" s="38"/>
-      <c r="D154" s="34"/>
+      <c r="D154" s="37"/>
       <c r="E154" s="38"/>
     </row>
     <row r="155" spans="1:5">
-      <c r="A155" s="35" t="s">
+      <c r="A155" s="36" t="s">
         <v>4883</v>
       </c>
       <c r="B155" s="32" t="s">
         <v>3603</v>
       </c>
       <c r="C155" s="38"/>
-      <c r="D155" s="34">
+      <c r="D155" s="37">
         <v>7</v>
       </c>
       <c r="E155" s="38" t="s">
@@ -36202,77 +36205,77 @@
       </c>
     </row>
     <row r="156" spans="1:5">
-      <c r="A156" s="35"/>
+      <c r="A156" s="36"/>
       <c r="B156" s="32" t="s">
         <v>4956</v>
       </c>
       <c r="C156" s="38"/>
-      <c r="D156" s="34"/>
+      <c r="D156" s="37"/>
       <c r="E156" s="38"/>
     </row>
     <row r="157" spans="1:5">
-      <c r="A157" s="35"/>
+      <c r="A157" s="36"/>
       <c r="B157" s="32" t="s">
         <v>3618</v>
       </c>
       <c r="C157" s="38"/>
-      <c r="D157" s="34"/>
+      <c r="D157" s="37"/>
       <c r="E157" s="38"/>
     </row>
     <row r="158" spans="1:5">
-      <c r="A158" s="35"/>
+      <c r="A158" s="36"/>
       <c r="B158" s="32" t="s">
         <v>4957</v>
       </c>
       <c r="C158" s="38"/>
-      <c r="D158" s="34"/>
+      <c r="D158" s="37"/>
       <c r="E158" s="38"/>
     </row>
     <row r="159" spans="1:5">
-      <c r="A159" s="35"/>
+      <c r="A159" s="36"/>
       <c r="B159" s="32" t="s">
         <v>4958</v>
       </c>
       <c r="C159" s="38"/>
-      <c r="D159" s="34"/>
+      <c r="D159" s="37"/>
       <c r="E159" s="38"/>
     </row>
     <row r="160" spans="1:5">
-      <c r="A160" s="35"/>
+      <c r="A160" s="36"/>
       <c r="B160" s="32" t="s">
         <v>3617</v>
       </c>
       <c r="C160" s="38"/>
-      <c r="D160" s="34"/>
+      <c r="D160" s="37"/>
       <c r="E160" s="38"/>
     </row>
     <row r="161" spans="1:5">
-      <c r="A161" s="35"/>
+      <c r="A161" s="36"/>
       <c r="B161" s="32" t="s">
         <v>3619</v>
       </c>
       <c r="C161" s="38"/>
-      <c r="D161" s="34"/>
+      <c r="D161" s="37"/>
       <c r="E161" s="38"/>
     </row>
     <row r="162" spans="1:5">
-      <c r="A162" s="35"/>
+      <c r="A162" s="36"/>
       <c r="B162" s="32" t="s">
         <v>3598</v>
       </c>
       <c r="C162" s="38"/>
-      <c r="D162" s="34"/>
+      <c r="D162" s="37"/>
       <c r="E162" s="38"/>
     </row>
     <row r="163" spans="1:5">
-      <c r="A163" s="35" t="s">
+      <c r="A163" s="36" t="s">
         <v>4934</v>
       </c>
       <c r="B163" s="32" t="s">
         <v>4934</v>
       </c>
       <c r="C163" s="38"/>
-      <c r="D163" s="34">
+      <c r="D163" s="37">
         <v>4</v>
       </c>
       <c r="E163" s="38" t="s">
@@ -36280,25 +36283,25 @@
       </c>
     </row>
     <row r="164" spans="1:5">
-      <c r="A164" s="35"/>
+      <c r="A164" s="36"/>
       <c r="B164" s="32" t="s">
         <v>3584</v>
       </c>
       <c r="C164" s="38"/>
-      <c r="D164" s="34"/>
+      <c r="D164" s="37"/>
       <c r="E164" s="38"/>
     </row>
     <row r="165" spans="1:5">
-      <c r="A165" s="35" t="s">
+      <c r="A165" s="36" t="s">
         <v>77</v>
       </c>
       <c r="B165" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="C165" s="35" t="s">
+      <c r="C165" s="36" t="s">
         <v>4925</v>
       </c>
-      <c r="D165" s="34">
+      <c r="D165" s="37">
         <v>6</v>
       </c>
       <c r="E165" s="38" t="s">
@@ -36306,32 +36309,32 @@
       </c>
     </row>
     <row r="166" spans="1:5">
-      <c r="A166" s="35"/>
+      <c r="A166" s="36"/>
       <c r="B166" s="32" t="s">
         <v>4986</v>
       </c>
-      <c r="C166" s="35"/>
-      <c r="D166" s="34"/>
+      <c r="C166" s="36"/>
+      <c r="D166" s="37"/>
       <c r="E166" s="38"/>
     </row>
     <row r="167" spans="1:5">
-      <c r="A167" s="35"/>
+      <c r="A167" s="36"/>
       <c r="B167" s="32" t="s">
         <v>4987</v>
       </c>
-      <c r="C167" s="35"/>
-      <c r="D167" s="34"/>
+      <c r="C167" s="36"/>
+      <c r="D167" s="37"/>
       <c r="E167" s="38"/>
     </row>
     <row r="168" spans="1:5">
-      <c r="A168" s="35" t="s">
+      <c r="A168" s="36" t="s">
         <v>3601</v>
       </c>
       <c r="B168" s="32" t="s">
         <v>3605</v>
       </c>
-      <c r="C168" s="35"/>
-      <c r="D168" s="34">
+      <c r="C168" s="36"/>
+      <c r="D168" s="37">
         <v>4</v>
       </c>
       <c r="E168" s="38" t="s">
@@ -36339,34 +36342,34 @@
       </c>
     </row>
     <row r="169" spans="1:5">
-      <c r="A169" s="35"/>
+      <c r="A169" s="36"/>
       <c r="B169" s="32" t="s">
         <v>3601</v>
       </c>
-      <c r="C169" s="35"/>
-      <c r="D169" s="34"/>
+      <c r="C169" s="36"/>
+      <c r="D169" s="37"/>
       <c r="E169" s="38"/>
     </row>
     <row r="170" spans="1:5">
-      <c r="A170" s="35"/>
+      <c r="A170" s="36"/>
       <c r="B170" s="32" t="s">
         <v>3632</v>
       </c>
-      <c r="C170" s="35"/>
-      <c r="D170" s="34"/>
+      <c r="C170" s="36"/>
+      <c r="D170" s="37"/>
       <c r="E170" s="38"/>
     </row>
     <row r="171" spans="1:5">
-      <c r="A171" s="35" t="s">
+      <c r="A171" s="36" t="s">
         <v>4938</v>
       </c>
       <c r="B171" s="32" t="s">
         <v>5000</v>
       </c>
-      <c r="C171" s="35" t="s">
+      <c r="C171" s="36" t="s">
         <v>4939</v>
       </c>
-      <c r="D171" s="34">
+      <c r="D171" s="37">
         <v>9</v>
       </c>
       <c r="E171" s="38" t="s">
@@ -36374,79 +36377,85 @@
       </c>
     </row>
     <row r="172" spans="1:5">
-      <c r="A172" s="35"/>
+      <c r="A172" s="36"/>
       <c r="B172" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="C172" s="35"/>
-      <c r="D172" s="34"/>
+      <c r="C172" s="36"/>
+      <c r="D172" s="37"/>
       <c r="E172" s="38"/>
     </row>
     <row r="173" spans="1:5">
-      <c r="A173" s="35"/>
+      <c r="A173" s="36"/>
       <c r="B173" s="32" t="s">
         <v>803</v>
       </c>
-      <c r="C173" s="35"/>
-      <c r="D173" s="34"/>
+      <c r="C173" s="36"/>
+      <c r="D173" s="37"/>
       <c r="E173" s="38"/>
     </row>
     <row r="174" spans="1:5">
-      <c r="A174" s="35"/>
+      <c r="A174" s="36"/>
       <c r="B174" s="32" t="s">
         <v>481</v>
       </c>
-      <c r="C174" s="35"/>
-      <c r="D174" s="34"/>
+      <c r="C174" s="36"/>
+      <c r="D174" s="37"/>
       <c r="E174" s="38"/>
     </row>
     <row r="175" spans="1:5">
-      <c r="A175" s="35"/>
+      <c r="A175" s="36"/>
       <c r="B175" s="32" t="s">
         <v>5001</v>
       </c>
-      <c r="C175" s="35"/>
-      <c r="D175" s="34"/>
+      <c r="C175" s="36"/>
+      <c r="D175" s="37"/>
       <c r="E175" s="38"/>
     </row>
     <row r="176" spans="1:5">
-      <c r="A176" s="35"/>
+      <c r="A176" s="36"/>
       <c r="B176" s="32" t="s">
         <v>5002</v>
       </c>
-      <c r="C176" s="35"/>
-      <c r="D176" s="34"/>
+      <c r="C176" s="36"/>
+      <c r="D176" s="37"/>
       <c r="E176" s="38"/>
     </row>
     <row r="177" spans="1:5">
-      <c r="A177" s="35"/>
+      <c r="A177" s="36"/>
       <c r="B177" s="32" t="s">
         <v>5003</v>
       </c>
-      <c r="C177" s="35"/>
-      <c r="D177" s="34"/>
+      <c r="C177" s="36"/>
+      <c r="D177" s="37"/>
       <c r="E177" s="38"/>
     </row>
     <row r="178" spans="1:5">
-      <c r="A178" s="35"/>
+      <c r="A178" s="36"/>
       <c r="B178" s="32" t="s">
         <v>3609</v>
       </c>
-      <c r="C178" s="35"/>
-      <c r="D178" s="34"/>
+      <c r="C178" s="36"/>
+      <c r="D178" s="37"/>
       <c r="E178" s="38"/>
     </row>
     <row r="179" spans="1:5">
-      <c r="A179" s="35"/>
+      <c r="A179" s="36"/>
       <c r="B179" s="32" t="s">
         <v>3622</v>
       </c>
-      <c r="C179" s="35"/>
-      <c r="D179" s="34"/>
+      <c r="C179" s="36"/>
+      <c r="D179" s="37"/>
       <c r="E179" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="122">
+    <mergeCell ref="E60:E67"/>
+    <mergeCell ref="D60:D67"/>
+    <mergeCell ref="E68:E76"/>
+    <mergeCell ref="E122:E123"/>
+    <mergeCell ref="D85:D87"/>
+    <mergeCell ref="E85:E87"/>
     <mergeCell ref="E152:E154"/>
     <mergeCell ref="D152:D154"/>
     <mergeCell ref="C3:C11"/>
@@ -36458,6 +36467,19 @@
     <mergeCell ref="C152:C164"/>
     <mergeCell ref="E163:E164"/>
     <mergeCell ref="E144:E146"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="D147:D151"/>
+    <mergeCell ref="E147:E151"/>
+    <mergeCell ref="D113:D121"/>
+    <mergeCell ref="E113:E121"/>
+    <mergeCell ref="D81:D84"/>
+    <mergeCell ref="E81:E84"/>
+    <mergeCell ref="D135:D137"/>
+    <mergeCell ref="E135:E137"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="D132:D134"/>
+    <mergeCell ref="E132:E134"/>
     <mergeCell ref="E171:E179"/>
     <mergeCell ref="E168:E170"/>
     <mergeCell ref="E27:E30"/>
@@ -36476,34 +36498,9 @@
     <mergeCell ref="E90:E103"/>
     <mergeCell ref="D165:D167"/>
     <mergeCell ref="E165:E167"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="E3:E6"/>
     <mergeCell ref="D138:D140"/>
     <mergeCell ref="E138:E140"/>
     <mergeCell ref="D122:D123"/>
-    <mergeCell ref="E122:E123"/>
-    <mergeCell ref="D85:D87"/>
-    <mergeCell ref="E85:E87"/>
-    <mergeCell ref="D147:D151"/>
-    <mergeCell ref="E147:E151"/>
-    <mergeCell ref="D113:D121"/>
-    <mergeCell ref="E113:E121"/>
-    <mergeCell ref="D81:D84"/>
-    <mergeCell ref="E81:E84"/>
-    <mergeCell ref="D135:D137"/>
-    <mergeCell ref="E135:E137"/>
-    <mergeCell ref="E60:E67"/>
-    <mergeCell ref="D60:D67"/>
-    <mergeCell ref="E68:E76"/>
-    <mergeCell ref="D68:D76"/>
-    <mergeCell ref="E77:E80"/>
-    <mergeCell ref="D77:D80"/>
-    <mergeCell ref="D109:D112"/>
-    <mergeCell ref="E109:E112"/>
-    <mergeCell ref="D56:D57"/>
-    <mergeCell ref="E56:E57"/>
-    <mergeCell ref="D132:D134"/>
-    <mergeCell ref="E132:E134"/>
     <mergeCell ref="E46:E49"/>
     <mergeCell ref="D50:D55"/>
     <mergeCell ref="E50:E55"/>
@@ -36523,6 +36520,11 @@
     <mergeCell ref="E12:E14"/>
     <mergeCell ref="E39:E41"/>
     <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D68:D76"/>
+    <mergeCell ref="E77:E80"/>
+    <mergeCell ref="D77:D80"/>
+    <mergeCell ref="D109:D112"/>
+    <mergeCell ref="E109:E112"/>
     <mergeCell ref="C171:C179"/>
     <mergeCell ref="D31:D34"/>
     <mergeCell ref="D35:D36"/>
@@ -36532,6 +36534,7 @@
     <mergeCell ref="C122:C123"/>
     <mergeCell ref="C147:C151"/>
     <mergeCell ref="C165:C170"/>
+    <mergeCell ref="D56:D57"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A152:A154"/>
     <mergeCell ref="A90:A103"/>
@@ -36542,6 +36545,9 @@
     <mergeCell ref="A27:A30"/>
     <mergeCell ref="A147:A151"/>
     <mergeCell ref="A165:A167"/>
+    <mergeCell ref="A155:A162"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A39:A41"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="A138:A140"/>
     <mergeCell ref="A88:A89"/>
@@ -36558,7 +36564,6 @@
     <mergeCell ref="A132:A134"/>
     <mergeCell ref="A60:A67"/>
     <mergeCell ref="A68:A76"/>
-    <mergeCell ref="A155:A162"/>
     <mergeCell ref="A42:A45"/>
     <mergeCell ref="A124:A131"/>
     <mergeCell ref="A46:A49"/>
@@ -36567,8 +36572,6 @@
     <mergeCell ref="A31:A34"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="A39:A41"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -80350,42 +80353,24 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{54E578DD-4B91-174F-989F-0E802D0A60C4}">
           <x14:formula1>
             <xm:f>全局设置!$C$2:$C$27</xm:f>
           </x14:formula1>
-          <xm:sqref>G1 G1002:G1048576</xm:sqref>
+          <xm:sqref>G1:G1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9EE230C8-61C8-6C48-853D-160F5581667A}">
           <x14:formula1>
             <xm:f>全局设置!$B$2:$B$8</xm:f>
           </x14:formula1>
-          <xm:sqref>H1 H1002:H1048576</xm:sqref>
+          <xm:sqref>H1:H1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{764CEB0A-D2BB-174C-A5D0-D49925FEDB38}">
           <x14:formula1>
             <xm:f>全局设置!$A$2:$A$34</xm:f>
           </x14:formula1>
-          <xm:sqref>B1 B1002:B1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{23A5AE10-0365-EB4D-A2D7-55A6A283A716}">
-          <x14:formula1>
-            <xm:f>'[企业列表（归类）(2).xlsx]全局设置'!#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1001</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{75272BEC-B307-1D4C-ACFC-057D87DA7933}">
-          <x14:formula1>
-            <xm:f>'[企业列表（归类）(2).xlsx]全局设置'!#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>H2:H1001</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BCEABDA3-4D7E-204E-8086-457EC9ADFD8D}">
-          <x14:formula1>
-            <xm:f>'[企业列表（归类）(2).xlsx]全局设置'!#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2:G1001</xm:sqref>
+          <xm:sqref>B1:B1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
